--- a/CommonData/DBbackup/DBExcel.xlsx
+++ b/CommonData/DBbackup/DBExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CDAC\CarPooling\CommonData\DBbackup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3A8418-0AEC-4C3F-8BFD-C4909DAD491D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1EC2A0-5D8F-4B43-B063-378CBAC974D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BA248422-9B8B-4CCB-87EB-00204EE48CE6}"/>
   </bookViews>
@@ -287,14 +287,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,29 +610,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6849F1C-9B66-4C88-A040-E2A81EEDAF74}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="7" max="7" width="11.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
       <c r="E1" s="1"/>
+      <c r="G1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -648,6 +655,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
@@ -663,6 +682,18 @@
         <v>7</v>
       </c>
       <c r="E3" s="1"/>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
@@ -678,6 +709,18 @@
         <v>9</v>
       </c>
       <c r="E4" s="1"/>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
@@ -739,6 +782,12 @@
         <v>9</v>
       </c>
       <c r="E8" s="1"/>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -754,6 +803,18 @@
         <v>9</v>
       </c>
       <c r="E9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
@@ -769,14 +830,52 @@
         <v>9</v>
       </c>
       <c r="E10" s="1"/>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
@@ -792,6 +891,18 @@
         <v>4</v>
       </c>
       <c r="E13" s="1"/>
+      <c r="G13" s="1">
+        <v>4</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
@@ -837,17 +948,49 @@
         <v>20</v>
       </c>
       <c r="E16" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="G16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
       <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
@@ -861,8 +1004,20 @@
         <v>4</v>
       </c>
       <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -876,8 +1031,20 @@
         <v>7</v>
       </c>
       <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -891,8 +1058,20 @@
         <v>16</v>
       </c>
       <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G21" s="1">
+        <v>4</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -906,8 +1085,20 @@
         <v>64</v>
       </c>
       <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G22" s="1">
+        <v>5</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -922,7 +1113,7 @@
       </c>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>5</v>
       </c>
@@ -937,7 +1128,7 @@
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>6</v>
       </c>
@@ -951,26 +1142,70 @@
         <v>9</v>
       </c>
       <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
       <c r="E26" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
+      <c r="G26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
       <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G28" s="1">
+        <v>2</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
@@ -984,8 +1219,18 @@
         <v>4</v>
       </c>
       <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G29" s="1">
+        <v>3</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -999,8 +1244,18 @@
         <v>7</v>
       </c>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>2</v>
       </c>
@@ -1015,7 +1270,7 @@
       </c>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>3</v>
       </c>
@@ -1075,12 +1330,12 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1139,321 +1394,31 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>1</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>2</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>1</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>2</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>3</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>4</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
-        <v>1</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
-        <v>2</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
-        <v>3</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
-        <v>4</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
-        <v>5</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="1">
-        <v>1</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="1">
-        <v>2</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="1">
-        <v>3</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="1">
-        <v>4</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D75" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="F47:I47"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B26:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/CommonData/DBbackup/DBExcel.xlsx
+++ b/CommonData/DBbackup/DBExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CDAC\CarPooling\CommonData\DBbackup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1EC2A0-5D8F-4B43-B063-378CBAC974D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6BF77B-8D57-4D4C-9E77-8E2D2E3547D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BA248422-9B8B-4CCB-87EB-00204EE48CE6}"/>
+    <workbookView xWindow="48" yWindow="996" windowWidth="22992" windowHeight="11964" xr2:uid="{BA248422-9B8B-4CCB-87EB-00204EE48CE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -287,14 +287,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,19 +627,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
       <c r="E1" s="1"/>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -782,12 +782,12 @@
         <v>9</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -858,12 +858,12 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
       <c r="G12" s="1">
         <v>3</v>
       </c>
@@ -895,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>6</v>
@@ -948,12 +948,12 @@
         <v>20</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="G17" s="1" t="s">
@@ -970,12 +970,12 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
       <c r="E18" s="1"/>
       <c r="G18" s="1">
         <v>1</v>
@@ -1142,20 +1142,20 @@
         <v>9</v>
       </c>
       <c r="E25" s="1"/>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="1"/>
       <c r="G26" s="1" t="s">
         <v>3</v>
@@ -1185,12 +1185,12 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="1"/>
       <c r="G28" s="1">
         <v>2</v>
@@ -1330,12 +1330,12 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
       <c r="E36" s="1"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1395,10 +1395,10 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F48" s="1"/>
